--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift</t>
+          <t>Generative AI, RAG, Glue, FastAPI, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Advisor Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Databricks, Redshift, PySpark, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>West Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929c63c7b49d2a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2ad5f93c602f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wise House Environmental Services</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Florida City, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Git, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Git, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff323c0a26171d0</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Git, BigQuery, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbcc02e72366f37a</t>
+          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - Business and Client Technologies</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Terraform, Git, Databricks, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301a167743eaea76</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Information Architect</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, Jenkins, Git, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edeb7aff112a65df</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac468301e46b588</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Innovation (Python/C#)</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Athena, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9e7d313daa0634</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer, Cell Quality &amp; Field Reliability</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Hadoop, Tableau, Matplotlib, Seaborn, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518128f7df0e4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Full Stack Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c6d81f5176e5</t>
+          <t>https://www.indeed.com/viewjob?jk=44e3b732f7459a25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Product Owner</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a3f977801b4e02</t>
+          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,1302 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7150df99e23411</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist (On-Site in Boston, MA)</t>
+          <t>Senior Engineer - Machine Learning</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26918c8b0d2ccfa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Machine Learning</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c109c1821e88ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Developer II - Digital Marketing Engineering</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, Git, Snowflake, Redshift, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68eab654fecceb1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Java Python AWS Developer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6a4c900363cd320</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Java Python AWS Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdd185d7be3165cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer, Product</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>brightwheel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Engineer – Financial Services Hybrid</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RiskSpan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, Glue, Redshift, CI/CD, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Snowflake Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Blue Cross of Idaho</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Meridian, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst - Digital and Ecommerce (Experimentation, Math/Stats, A/B testing, ML)(Remote Or Hybrid)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=105183f59f52cc9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ally Financial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de192234825a9848</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer- Senior Consultant Level</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, TensorFlow, Git, Python, R, Java, Bayesian</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f82d993c6610863</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd2df3bd6bdc24bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9f4cf3b9c7fa0e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=461827cbf86d5e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Royal Oak, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e49e9973bd7a0b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f798bcc0fb2923f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cayuse</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3410b7fe8c81f3f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INFINITE ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lewisville, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75dd65001f023a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior AWS Connect Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Glue, Athena, Kinesis, Snowflake, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db0b7ba208d58fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Joby Aviation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Carlos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f03d5bb55448708</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Software Engineer/ Embedded Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>iTechEdgeCorp</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3ae16a9116760fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior DevOps/SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SEI Investments Developments</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff05a337dfa6fa5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Graph Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ARDENT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, Data Lake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec6e9bf6850e341b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>City of Hope</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, XGBoost, LightGBM, Seaborn, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33fae087b4ac3d58</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, MLflow, Docker, Git, Python, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb63c09daa350d4</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafed5560a4620b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Digitalization Systems Engineer - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=413200b123876cde</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XIM, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aba3091f5c8a0e6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ancestry</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, EC2, CI/CD, Terraform, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d642a24eae303ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; AI Engineer - Medicine</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UC San Diego Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=548be3ca473f0192</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III -Python Fullstack - AI/ML</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62987967b43ce44c</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Python, AWS, GenAI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e9e9e50759bf0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5febcd3c8423ff9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RSA Conference</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3182036ec0feec7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Western Alliance Bank</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff3bf81f1e6ad7ec</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Data Scientist – AI / LLM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4eea41277bdff1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Data scientist - Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HFB Technologies</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saint George, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05e442e3e948ace</t>
+          <t>https://www.indeed.com/viewjob?jk=d598675e34cafd05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Omni Solutions Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, EC2, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=57dbef34abd449d2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Agentic Security Automation Engineer</t>
+          <t>AI / GenAI / LLM Engineer Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NowSecure</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e298efd3f75bef97</t>
+          <t>https://www.indeed.com/viewjob?jk=cd88e83a0798af74</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI / GenAI / LLM Engineer Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf185f632363c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2af535a8530de17e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, AGI Platform</t>
+          <t>Engineer 2 - Inventory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JazzX AI</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Altos, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,322 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c57cf2baff777a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=39bb63ad6b6acd95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Pricing &amp; Promotions Analytics</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b16901ab9e927c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea3a3d61f083af63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Pricing &amp; Promotions Analytics</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dd89c8218c5367</t>
+          <t>https://www.indeed.com/viewjob?jk=6b301a2fcc7892dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Onboarding &amp; Engagement Marketing Analytics</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>CoBank</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Greenwood Village, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9714cac24339dd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Origami Risk LLC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Data Lake, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Cortex, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d06fa2021b7da604</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef10e31278d7d73e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Loyalty Technology</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62d8152ef45c762f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - USDS Shop Ads</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TikTok USDS JV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8c8d3ce39b3fb5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - USDS Shop Ads</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TikTok USDS JV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ace26dbcd780b772</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=878045e4bd010d1f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist – AI / LLM</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diagonal Matrix Ltd</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, FastAPI</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,54 +496,54 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4eea41277bdff1</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data scientist - Agentic AI</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d598675e34cafd05</t>
+          <t>https://www.indeed.com/viewjob?jk=3760cdb15926257d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Omni Solutions Services</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dbef34abd449d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fe5c33f2abd43f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI / GenAI / LLM Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diagonal Matrix Ltd</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
+          <t>RAG, S3, Data Lake, Git, Snowflake, Databricks, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd88e83a0798af74</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI / GenAI / LLM Engineer Intern</t>
+          <t>Software Engineer .Net/AI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diagonal Matrix Ltd</t>
+          <t>Optivate Health, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
+          <t>RAG, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD, Git, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af535a8530de17e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dfd06c8da7beb6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer 2 - Inventory</t>
+          <t>Sr Data Scientist - Precision Medicine Clinical AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Johns Hopkins Health System</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Prompt Engineering, Azure ML, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,322 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bb63ad6b6acd95</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Platform Engineer I</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Blackhawk Network</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea3a3d61f083af63</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Platform Engineer I</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blackhawk Network</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Coppell, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b301a2fcc7892dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CoBank</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Greenwood Village, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9714cac24339dd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Origami Risk LLC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Data Lake, CI/CD, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef10e31278d7d73e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Loyalty Technology</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62d8152ef45c762f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - USDS Shop Ads</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TikTok USDS JV</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c8d3ce39b3fb5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - USDS Shop Ads</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TikTok USDS JV</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ace26dbcd780b772</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=878045e4bd010d1f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf584f808da3d7f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Customer Data Products)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, FastAPI, Docker</t>
+          <t>Data Scientist, Generative AI, Pinecone, Redshift, Data Lake, CI/CD, Git, Redshift, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Security Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3760cdb15926257d</t>
+          <t>https://www.indeed.com/viewjob?jk=0732962234af33bb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>Hadoop Big Data Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fe5c33f2abd43f</t>
+          <t>https://www.indeed.com/viewjob?jk=635e7f9a2dfdee8f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Hadoop Big Data Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Git, Snowflake, Databricks, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0b257d934f9a52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer .Net/AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optivate Health, LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bonita Springs, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD, Git, R</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,637 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dfd06c8da7beb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Precision Medicine Clinical AI</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Johns Hopkins Health System</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Hadoop, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer- Generative AI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e631c45e584f001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57f90e8db4d1660f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04f1d8c33d591f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Cortex, CI/CD, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820142d0f04c3748</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SecDevOps Engineer (Mid-Level 3)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knox Systems</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b57f128793c5b9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer - SMB (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Enova International</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e9ae7ea4069f76e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Edmonds, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cf01e63f8bba41a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Conversational AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f920ac09c7b6c650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c560886c61545134</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab30619a0156bf36</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Prompt Engineering, Azure ML, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf584f808da3d7f</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Backend Engineer (PHP/Laravel)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MD Integrations</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faae444187ec85ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C&amp;W Services</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f1a6b9f51091b0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21e46c00e098e6fa</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Customer Data Products)</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Pinecone, Redshift, Data Lake, CI/CD, Git, Redshift, PySpark, Kafka</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Security Engineer III - AI/ML</t>
+          <t>Sn. Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, Copilot, FastAPI, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732962234af33bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b387d26a56f58a54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>DATABASE ENGINEER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635e7f9a2dfdee8f</t>
+          <t>https://www.indeed.com/viewjob?jk=876797a87867dc04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>Senior Database Engineer (DBRE)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0b257d934f9a52</t>
+          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Newport News, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6141615deb82e11f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Senior ML Developer (Java, AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Hadoop, NoSQL</t>
+          <t>AWS SageMaker, S3, Docker, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e65217fd83589ec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, Docker, Kubernetes, AKS, Snowflake, PostgreSQL, Power BI, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+          <t>https://www.indeed.com/viewjob?jk=85933ef3997d0a97</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Training Equipment Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Kafka, Hadoop, MySQL, NoSQL, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e631c45e584f001</t>
+          <t>https://www.indeed.com/viewjob?jk=eb76c3eb096b9290</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Jenkins, Terraform, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57f90e8db4d1660f</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>C&amp;W Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1d8c33d591f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8067db6fbad85781</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Engineering &amp; Operations</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Cortex, CI/CD, Snowflake, Databricks, Python, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820142d0f04c3748</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SecDevOps Engineer (Mid-Level 3)</t>
+          <t>Snr. Drupal Full Stack Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Knox Systems</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>FastAPI, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,322 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b57f128793c5b9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer - SMB (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Enova International</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9ae7ea4069f76e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Edmonds, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf01e63f8bba41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Conversational AI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f920ac09c7b6c650</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NFI Industries</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c560886c61545134</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab30619a0156bf36</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Backend Engineer (PHP/Laravel)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MD Integrations</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faae444187ec85ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>C&amp;W Services</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1a6b9f51091b0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21e46c00e098e6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a198736c30632b7d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-02.xlsx
+++ b/daily_matches/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Senior Back End Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, FAISS, Pinecone</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdfdba6088681ad1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sn. Infrastructure Engineer</t>
+          <t>Senior Back End Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b387d26a56f58a54</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd321a711019612</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DATABASE ENGINEER</t>
+          <t>Senior Data Scientist II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, spaCy, Gensim, EC2, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876797a87867dc04</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fe94110a3a823c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (DBRE)</t>
+          <t>Senior Data Scientist II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, Python, SQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, spaCy, Gensim, EC2, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
+          <t>https://www.indeed.com/viewjob?jk=8efe739dd0e3b1e1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer III, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newport News, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6141615deb82e11f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7bf98e7d0a7b72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML Developer (Java, AWS)</t>
+          <t>Machine Learning Engineer IV, Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS SageMaker, S3, Docker, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e65217fd83589ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9782b0c60dcca5ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Machine Learning Engineer III, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, AKS, Snowflake, PostgreSQL, Power BI, SQL, R, Java</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=883158f62af228a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Machine Learning Engineer IV, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=267bd912238c2979</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Digital - Forward Deployed Engineer (FDE) - Intelligent Automation - Associate Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Virtru</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85933ef3997d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=fa925cff1423a674</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Training Equipment Data Scientist</t>
+          <t>Data Engineer - Senior Consultant level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kafka, Hadoop, MySQL, NoSQL, Seaborn, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Kafka, Hadoop, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb76c3eb096b9290</t>
+          <t>https://www.indeed.com/viewjob?jk=44e746c673941c40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Terraform, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C&amp;W Services</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8067db6fbad85781</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,532 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=fc641b8cb90fe097</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snr. Drupal Full Stack Developer</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EC2, Glue, Athena, Docker, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SWBC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfbbdabc3912f8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db969775febf5e34</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MGR - SOFTWARE ENGINEERING</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sunrise Banks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Curi Bio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=839f6cb408a9ad70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Hardware &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>oura</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0c6767bdba48a7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Training Equipment Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pensacola, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kafka, Hadoop, MySQL, NoSQL, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b0909825161d9c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Platform Backend Engineer - Battery Storage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plus Power</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56157f2cbfdcf9c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Platform Backend Engineer - Battery Storage</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Plus Power</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f2c63c6184e7d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Platform Backend Engineer - Battery Storage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plus Power</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a131cee381ad04df</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Platform Backend Engineer - Battery Storage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plus Power</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>West Palm Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c052f7d306ef178</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Arden Hills, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>FastAPI, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a198736c30632b7d</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Snowflake, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de29e6558218e76e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack, Level 4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cacc658263bb0dc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack, Level 5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b93f6c797384a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610732fdf37d434e</t>
         </is>
       </c>
     </row>
